--- a/bulky_upload_files/correct_yamurai_insights_upoad_template.xlsx
+++ b/bulky_upload_files/correct_yamurai_insights_upoad_template.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeremiah.muchazondid\Desktop\omnicontact-projects\OMNI-PMS-SYSTEM\OMNI-PMS-BACKEND\bulky_upload_files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8CF798A-559C-4440-A048-33032869CCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10704" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="10020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -56,7 +34,7 @@
     <t>aes</t>
   </si>
   <si>
-    <t>resolved_count</t>
+    <t>resolved_queries</t>
   </si>
   <si>
     <t>csat</t>
@@ -65,7 +43,7 @@
     <t>calc_aes</t>
   </si>
   <si>
-    <t>calc_resolved_count</t>
+    <t>calc_resolved_queries</t>
   </si>
   <si>
     <t>calc_csat</t>
@@ -110,13 +88,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -124,24 +108,361 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -149,26 +470,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -217,7 +824,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -252,7 +859,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -426,586 +1033,582 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.85546875" style="1"/>
-    <col min="7" max="7" width="20.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="11.712962962963" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="6" width="8.85185185185185" style="2"/>
+    <col min="7" max="7" width="20.712962962963" style="2" customWidth="1"/>
+    <col min="8" max="9" width="8.85185185185185" style="2"/>
+    <col min="10" max="10" width="26.287037037037" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.85185185185185" style="2"/>
+    <col min="12" max="12" width="14.712962962963" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.287037037037" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.712962962963" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.712962962963" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="8.85185185185185" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="15">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="14.4" spans="1:16">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" ht="15.6" spans="1:16">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>2024</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
         <v>45</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>32</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>66</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>78</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>33</v>
       </c>
-      <c r="K2" s="1">
-        <v>4</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="K2" s="2">
+        <v>4</v>
+      </c>
+      <c r="L2" s="2">
         <v>6</v>
       </c>
-      <c r="M2" s="1">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1">
-        <v>2</v>
-      </c>
-      <c r="O2" s="1">
-        <v>4</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>4</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" ht="15.6" spans="1:16">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>2024</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
         <v>454</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>32</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>66</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <v>78</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>33</v>
       </c>
-      <c r="K3" s="1">
-        <v>4</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="K3" s="2">
+        <v>4</v>
+      </c>
+      <c r="L3" s="2">
         <v>6</v>
       </c>
-      <c r="M3" s="1">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1">
-        <v>2</v>
-      </c>
-      <c r="O3" s="1">
-        <v>4</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" ht="15.6" spans="1:16">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>2024</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
         <v>334</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>32</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>66</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2">
         <v>78</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>33</v>
       </c>
-      <c r="K4" s="1">
-        <v>4</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="K4" s="2">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2">
         <v>6</v>
       </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2</v>
-      </c>
-      <c r="O4" s="1">
-        <v>4</v>
-      </c>
-      <c r="P4" s="1" t="s">
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2">
+        <v>2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>4</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" ht="15.6" spans="1:16">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>2024</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
         <v>43</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>32</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>66</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <v>78</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>33</v>
       </c>
-      <c r="K5" s="1">
-        <v>4</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
+      <c r="L5" s="2">
         <v>6</v>
       </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>2</v>
-      </c>
-      <c r="O5" s="1">
-        <v>4</v>
-      </c>
-      <c r="P5" s="1" t="s">
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2">
+        <v>2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>4</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" ht="15.6" spans="1:16">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>2024</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
         <v>32</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>32</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>66</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <v>78</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>33</v>
       </c>
-      <c r="K6" s="1">
-        <v>4</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2">
         <v>6</v>
       </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>2</v>
-      </c>
-      <c r="O6" s="1">
-        <v>4</v>
-      </c>
-      <c r="P6" s="1" t="s">
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>4</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="1">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" ht="15.6" spans="1:16">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>2024</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
         <v>355</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>32</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>66</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>78</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>33</v>
       </c>
-      <c r="K7" s="1">
-        <v>4</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
         <v>6</v>
       </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>2</v>
-      </c>
-      <c r="O7" s="1">
-        <v>4</v>
-      </c>
-      <c r="P7" s="1" t="s">
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2</v>
+      </c>
+      <c r="O7" s="2">
+        <v>4</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" ht="15.6" spans="1:16">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>2024</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
         <v>56</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>32</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>66</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>78</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>33</v>
       </c>
-      <c r="K8" s="1">
-        <v>4</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="K8" s="2">
+        <v>4</v>
+      </c>
+      <c r="L8" s="2">
         <v>6</v>
       </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1">
-        <v>2</v>
-      </c>
-      <c r="O8" s="1">
-        <v>4</v>
-      </c>
-      <c r="P8" s="1" t="s">
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2</v>
+      </c>
+      <c r="O8" s="2">
+        <v>4</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" ht="15.6" spans="1:16">
+      <c r="A9" s="2">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>2024</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
         <v>54</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="2">
         <v>32</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>66</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="2">
         <v>78</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>33</v>
       </c>
-      <c r="K9" s="1">
-        <v>4</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="2">
         <v>6</v>
       </c>
-      <c r="M9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
-        <v>2</v>
-      </c>
-      <c r="O9" s="1">
-        <v>4</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
+        <v>2</v>
+      </c>
+      <c r="O9" s="2">
+        <v>4</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="1">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="10" ht="15.6" spans="1:16">
+      <c r="A10" s="2">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>2024</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
         <v>333</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>32</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>66</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="2">
         <v>78</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>33</v>
       </c>
-      <c r="K10" s="1">
-        <v>4</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K10" s="2">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2">
         <v>6</v>
       </c>
-      <c r="M10" s="1">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1">
-        <v>2</v>
-      </c>
-      <c r="O10" s="1">
-        <v>4</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>4</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="1">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="11" ht="15.6" spans="1:16">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>2024</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
         <v>234</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>32</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>66</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="2">
         <v>78</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>33</v>
       </c>
-      <c r="K11" s="1">
-        <v>4</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="K11" s="2">
+        <v>4</v>
+      </c>
+      <c r="L11" s="2">
         <v>6</v>
       </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
-        <v>2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>4</v>
-      </c>
-      <c r="P11" s="1" t="s">
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2</v>
+      </c>
+      <c r="O11" s="2">
+        <v>4</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/bulky_upload_files/correct_yamurai_insights_upoad_template.xlsx
+++ b/bulky_upload_files/correct_yamurai_insights_upoad_template.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Omni-projects\OMNI-PMS-BACKEND\bulky_upload_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>user</t>
   </si>
@@ -83,19 +88,16 @@
   </si>
   <si>
     <t>HVC</t>
+  </si>
+  <si>
+    <t>February</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,353 +118,16 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -470,312 +135,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1033,30 +412,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.712962962963" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="6" width="8.85185185185185" style="2"/>
-    <col min="7" max="7" width="20.712962962963" style="2" customWidth="1"/>
-    <col min="8" max="9" width="8.85185185185185" style="2"/>
-    <col min="10" max="10" width="26.287037037037" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.85185185185185" style="2"/>
-    <col min="12" max="12" width="14.712962962963" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.287037037037" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14.712962962963" style="2" customWidth="1"/>
-    <col min="15" max="15" width="16.712962962963" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.85185185185185" style="2"/>
+    <col min="3" max="6" width="8.88671875" style="2"/>
+    <col min="7" max="7" width="20.6640625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="2"/>
+    <col min="10" max="10" width="26.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="2"/>
+    <col min="12" max="12" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.4" spans="1:16">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,9 +485,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:16">
+    <row r="2" spans="1:16" ht="15.6">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
@@ -1126,10 +505,10 @@
         <v>45</v>
       </c>
       <c r="G2" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H2" s="2">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2">
         <v>78</v>
@@ -1156,9 +535,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="15.6" spans="1:16">
+    <row r="3" spans="1:16" ht="15.6">
       <c r="A3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
@@ -1176,22 +555,22 @@
         <v>454</v>
       </c>
       <c r="G3" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="2">
         <v>1</v>
@@ -1206,9 +585,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="15.6" spans="1:16">
+    <row r="4" spans="1:16" ht="15.6">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1226,22 +605,22 @@
         <v>334</v>
       </c>
       <c r="G4" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J4" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2">
         <v>1</v>
@@ -1256,9 +635,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="15.6" spans="1:16">
+    <row r="5" spans="1:16" ht="15.6">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1276,22 +655,22 @@
         <v>43</v>
       </c>
       <c r="G5" s="2">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="H5" s="2">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I5" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J5" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2">
         <v>1</v>
@@ -1306,9 +685,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="15.6" spans="1:16">
+    <row r="6" spans="1:16" ht="15.6">
       <c r="A6" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1326,22 +705,22 @@
         <v>32</v>
       </c>
       <c r="G6" s="2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I6" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M6" s="2">
         <v>1</v>
@@ -1356,9 +735,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="15.6" spans="1:16">
+    <row r="7" spans="1:16" ht="15.6">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1379,19 +758,19 @@
         <v>32</v>
       </c>
       <c r="H7" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I7" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J7" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K7" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M7" s="2">
         <v>1</v>
@@ -1406,9 +785,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="15.6" spans="1:16">
+    <row r="8" spans="1:16" ht="15.6">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1417,31 +796,31 @@
         <v>2024</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J8" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K8" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L8" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M8" s="2">
         <v>1</v>
@@ -1456,9 +835,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="15.6" spans="1:16">
+    <row r="9" spans="1:16" ht="15.6">
       <c r="A9" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>22</v>
@@ -1467,31 +846,31 @@
         <v>2024</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G9" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="I9" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J9" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K9" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L9" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M9" s="2">
         <v>1</v>
@@ -1506,9 +885,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="15.6" spans="1:16">
+    <row r="10" spans="1:16" ht="15.6">
       <c r="A10" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
@@ -1517,31 +896,31 @@
         <v>2024</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>333</v>
+        <v>877</v>
       </c>
       <c r="G10" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J10" s="2">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K10" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L10" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2">
         <v>1</v>
@@ -1556,9 +935,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="15.6" spans="1:16">
+    <row r="11" spans="1:16" ht="15.6">
       <c r="A11" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
@@ -1567,31 +946,31 @@
         <v>2024</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="G11" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J11" s="2">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K11" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L11" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M11" s="2">
         <v>1</v>
@@ -1606,9 +985,108 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12" spans="1:16" ht="15.6">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>222</v>
+      </c>
+      <c r="G12" s="2">
+        <v>65</v>
+      </c>
+      <c r="H12" s="2">
+        <v>88</v>
+      </c>
+      <c r="I12" s="2">
+        <v>88</v>
+      </c>
+      <c r="J12" s="2">
+        <v>43</v>
+      </c>
+      <c r="K12" s="2">
+        <v>14</v>
+      </c>
+      <c r="L12" s="2">
+        <v>16</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2">
+        <v>2</v>
+      </c>
+      <c r="O12" s="2">
+        <v>4</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.6">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>444</v>
+      </c>
+      <c r="G13" s="2">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2">
+        <v>89</v>
+      </c>
+      <c r="I13" s="2">
+        <v>89</v>
+      </c>
+      <c r="J13" s="2">
+        <v>44</v>
+      </c>
+      <c r="K13" s="2">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>17</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2">
+        <v>2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>4</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>